--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260817_tarde.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260817_tarde.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\projetos\ofi\dados\SURVEY_VESSELS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="967" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52DE728F-8823-45A8-A98A-2DB8F5852BBF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841D1239-BD2A-47A0-B524-FD302F5051CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="cbo" sheetId="2" r:id="rId2"/>
     <sheet name="bram" sheetId="3" r:id="rId3"/>
     <sheet name="starnav" sheetId="4" r:id="rId4"/>
-    <sheet name="oceanpact" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
   <si>
     <t>cbo</t>
   </si>
@@ -238,9 +237,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>ilha de santana</t>
   </si>
 </sst>
 </file>
@@ -643,15 +639,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490C43E3-ED93-4C78-B9B5-276EDD51C5AB}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -665,7 +661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -679,7 +675,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -693,7 +689,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -707,7 +703,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -721,7 +717,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -735,7 +731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -749,7 +745,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -763,7 +759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -777,7 +773,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -791,7 +787,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -805,7 +801,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -819,7 +815,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -833,7 +829,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -847,7 +843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -861,7 +857,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -872,7 +868,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -883,7 +879,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -894,7 +890,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -902,7 +898,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -910,17 +906,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -933,19 +929,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DC0AFA-9444-4F11-ABC1-7475EEC3A448}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="1" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.33203125" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +967,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -983,7 +979,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -995,7 +991,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1007,7 +1003,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1019,7 +1015,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1031,7 +1027,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1043,7 +1039,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -1055,7 +1051,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1067,7 +1063,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1079,7 +1075,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1091,7 +1087,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1103,7 +1099,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -1115,7 +1111,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1127,7 +1123,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1139,7 +1135,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1151,7 +1147,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1163,7 +1159,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1175,7 +1171,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1187,7 +1183,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1199,7 +1195,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1211,7 +1207,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1224,7 +1220,7 @@
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1236,10 +1232,10 @@
       <c r="H23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1248,7 +1244,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1257,7 +1253,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J27" s="1"/>
     </row>
   </sheetData>
@@ -1271,20 +1267,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B80E83-9236-40C9-95ED-72F039A44EB0}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1310,7 +1306,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1321,7 +1317,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1332,7 +1328,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1343,7 +1339,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1354,7 +1350,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1365,7 +1361,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1376,7 +1372,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1387,7 +1383,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1398,7 +1394,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1409,7 +1405,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1420,7 +1416,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1432,7 +1428,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1444,7 +1440,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1456,7 +1452,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1468,19 +1464,19 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J22" s="1"/>
     </row>
   </sheetData>
@@ -1492,21 +1488,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0244D8-3EC3-425D-A328-9D6A0DAB3C45}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1532,7 +1528,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1544,7 +1540,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1556,7 +1552,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1568,7 +1564,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1580,7 +1576,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1592,7 +1588,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1604,7 +1600,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1614,7 +1610,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1626,7 +1622,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1638,7 +1634,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -1650,7 +1646,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1663,7 +1659,7 @@
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1675,7 +1671,7 @@
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1686,7 +1682,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1697,7 +1693,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1708,7 +1704,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1719,7 +1715,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1733,56 +1729,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF7ACA0-AD48-46B4-B354-9966CDC48538}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="6"/>
-      <c r="H2" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>